--- a/src/rodos_corpus/data/corpus/rendered/production/PPR-2026.xlsx
+++ b/src/rodos_corpus/data/corpus/rendered/production/PPR-2026.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>08.02, 09.05, 07.08, 05.11</t>
+          <t>13.02, 14.05, 12.08, 10.11</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21.01, 22.03, 21.05, 20.07, 18.09, 17.11</t>
+          <t>31.01, 01.04, 31.05, 30.07, 28.09, 27.11</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>06.02, 07.04, 06.06, 05.08, 04.10, 03.12</t>
+          <t>20.01, 21.03, 20.05, 19.07, 17.09, 16.11</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18.01, 18.05, 15.09</t>
+          <t>07.02, 07.06, 05.10</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18.01, 19.03, 18.05, 17.07, 15.09, 14.11</t>
+          <t>16.01, 17.03, 16.05, 15.07, 13.09, 12.11</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>07.02, 08.05, 06.08, 04.11</t>
+          <t>31.01, 01.05, 30.07, 28.10</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>31.01, 01.05, 30.07, 28.10</t>
+          <t>18.01, 18.04, 17.07, 15.10</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>23.01, 09.03, 23.04, 07.06, 22.07, 05.09…</t>
+          <t>12.02, 29.03, 13.05, 27.06, 11.08, 25.09…</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>13.02, 30.03, 14.05, 28.06, 12.08, 26.09…</t>
+          <t>17.01, 03.03, 17.04, 01.06, 16.07, 30.08…</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>19.01, 18.02, 20.03, 19.04, 19.05, 18.06…</t>
+          <t>08.02, 10.03, 09.04, 09.05, 08.06, 08.07…</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>21.01, 20.02, 22.03, 21.04, 21.05, 20.06…</t>
+          <t>30.01, 01.03, 31.03, 30.04, 30.05, 29.06…</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>18.01, 18.04, 17.07, 15.10</t>
+          <t>10.02, 11.05, 09.08, 07.11</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>24.01, 25.03, 24.05, 23.07, 21.09, 20.11</t>
+          <t>21.01, 22.03, 21.05, 20.07, 18.09, 17.11</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">

--- a/src/rodos_corpus/data/corpus/rendered/production/PPR-2026.xlsx
+++ b/src/rodos_corpus/data/corpus/rendered/production/PPR-2026.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>13.02, 14.05, 12.08, 10.11</t>
+          <t>24.01, 24.04, 23.07, 21.10</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>31.01, 01.04, 31.05, 30.07, 28.09, 27.11</t>
+          <t>26.01, 27.03, 26.05, 25.07, 23.09, 22.11</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20.01, 21.03, 20.05, 19.07, 17.09, 16.11</t>
+          <t>04.02, 05.04, 04.06, 03.08, 02.10, 01.12</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>07.02, 07.06, 05.10</t>
+          <t>13.02, 13.06, 11.10</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>16.01, 17.03, 16.05, 15.07, 13.09, 12.11</t>
+          <t>05.02, 06.04, 05.06, 04.08, 03.10, 02.12</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>31.01, 01.05, 30.07, 28.10</t>
+          <t>16.01, 16.04, 15.07, 13.10</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>18.01, 18.04, 17.07, 15.10</t>
+          <t>04.02, 05.05, 03.08, 01.11</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>17.01, 03.03, 17.04, 01.06, 16.07, 30.08…</t>
+          <t>20.01, 06.03, 20.04, 04.06, 19.07, 02.09…</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>08.02, 10.03, 09.04, 09.05, 08.06, 08.07…</t>
+          <t>24.01, 23.02, 25.03, 24.04, 24.05, 23.06…</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>30.01, 01.03, 31.03, 30.04, 30.05, 29.06…</t>
+          <t>20.01, 19.02, 21.03, 20.04, 20.05, 19.06…</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>10.02, 11.05, 09.08, 07.11</t>
+          <t>20.01, 20.04, 19.07, 17.10</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>21.01, 22.03, 21.05, 20.07, 18.09, 17.11</t>
+          <t>13.02, 14.04, 13.06, 12.08, 11.10, 10.12</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
